--- a/Mass_update_KAIKU/mass_update_kaiku_quantity_fix.xlsx
+++ b/Mass_update_KAIKU/mass_update_kaiku_quantity_fix.xlsx
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJb</t>
+          <t>a0R3g0000080gIw</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -481,7 +481,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KAIKU 1 MODULE SUBSCRIPTION</t>
+          <t>KAIKU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJq</t>
+          <t>a0R3g0000080gJb</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -501,7 +501,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
+          <t>KAIKU 1 MODULE SUBSCRIPTION</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0R3g0000095FZo</t>
+          <t>a0R3g0000080gJl</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
+          <t>KAIKU SOFTWARE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJl</t>
+          <t>a0R3g0000080gJq</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KAIKU SOFTWARE</t>
+          <t>MODULE FOR RADIOTHERAPY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0R3g0000080gIw</t>
+          <t>a0R3g0000095FZo</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KAIKU</t>
+          <t>MODULE FOR RADIOTHERAPY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/Mass_update_KAIKU/mass_update_kaiku_quantity_fix.xlsx
+++ b/Mass_update_KAIKU/mass_update_kaiku_quantity_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,186 +450,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>a0R3g0000095Fpm</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MODULE FOR IMMUNOTHERAPY</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10420_KAIKU_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>a0R3g0000080gIw</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>KAIKU</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>12213_KAI01_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>a0R3g0000080gJb</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KAIKU 1 MODULE SUBSCRIPTION</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12213_KAI01_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>a0R3g0000080gJW</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>KAIKU-IMPLEMENTATION</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>12213_KAI01_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>a0R3g0000080gJl</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>KAIKU SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>12213_KAI01_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>a0R3g0000080gJq</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>12213_KAI01_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>a0R3g0000095FZo</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>12213_KAI01_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>a0RKf00000HoQ8X</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>KAIKU</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>12619_KAI001_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>a0RKf00000HoQ8c</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>KAIKU SOFTWARE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>12619_KAI001_2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
